--- a/2026-09-25-correo-creator-business-score/hoja/creator-business-score-leads.xlsx
+++ b/2026-09-25-correo-creator-business-score/hoja/creator-business-score-leads.xlsx
@@ -8997,7 +8997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9028,145 +9028,153 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Columnas moradas: las rellena el formulario. Columnas oscuras: las escribe el script. No renombres los encabezados.</t>
+          <t>Columnas moradas: las rellena el formulario. Columnas oscuras: las escribe el script (nunca toca las moradas). No renombres los encabezados.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Comparte esta hoja con el equipo solo como Lector o Comentador: quien puede editarla puede cambiar el script.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Qué significa</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>(vacío)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Pendiente: se enviará en la próxima pasada.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>enviando</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Enviándose ahora mismo.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>enviado</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Correo enviado. La hora está en "Enviado".</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Falló el envío (ver Detalle). Se reintenta solo hasta 3 veces.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>incompleto</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Alguna respuesta no coincide con las opciones (ver Detalle). Corrígela y vacía Estado.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>omitido</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
-          <t>El correo no es válido. Corrígelo y vacía Estado.</t>
+          <t>El correo está vacío o no es válido. Corrígelo y vacía Estado.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>duplicado</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Ese ID de lead ya recibió su correo en otra fila.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>revisar</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Se cortó mientras se enviaba: puede que haya salido. Revísalo y vacía Estado para reenviar.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-    </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Reenviar</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Vacía la celda Estado de la fila (o menú Creator Business Score → Reenviar la fila seleccionada).</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Puntaje</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>"Puntaje" es el que ve el lead (con el relleno de la landing). "Puntaje real" es el que decide calificación, caso y UTMs.</t>
         </is>
